--- a/Project_ETF/ETF_Investment_Portfolio/009819/ETF_Investment_Portfolio_20260603.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/009819/ETF_Investment_Portfolio_20260603.xlsx
@@ -611,100 +611,100 @@
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>135,895</t>
+          <t>147,765</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>30.23%</t>
+          <t>30.53%</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>ORCL US</t>
+          <t>C_NTD</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>甲骨文公司</t>
+          <t>CASH</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>98,770</t>
+          <t>1,070,586,655</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>11.17%</t>
+          <t>14.68%</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>C_NTD</t>
+          <t>ORCL US</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>CASH</t>
+          <t>甲骨文公司</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>544,790,969</t>
+          <t>107,270</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>8.00%</t>
+          <t>10.65%</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>GEV US</t>
+          <t>MRVL US</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>奇異維諾瓦公司</t>
+          <t>Marvell Technology Inc</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>15,405</t>
+          <t>54,555</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>6.91%</t>
+          <t>7.09%</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>MRVL US</t>
+          <t>GEV US</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>Marvell Technology Inc</t>
+          <t>奇異維諾瓦公司</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>50,105</t>
+          <t>16,755</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>6.74%</t>
+          <t>6.93%</t>
         </is>
       </c>
     </row>
@@ -721,12 +721,12 @@
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>119,595</t>
+          <t>129,695</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>4.74%</t>
+          <t>4.73%</t>
         </is>
       </c>
     </row>
@@ -743,12 +743,12 @@
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>58,740</t>
+          <t>63,880</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>3.47%</t>
+          <t>3.25%</t>
         </is>
       </c>
     </row>
@@ -765,12 +765,12 @@
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>5,595</t>
+          <t>6,105</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>2.77%</t>
+          <t>2.83%</t>
         </is>
       </c>
     </row>
@@ -787,12 +787,12 @@
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>64,655</t>
+          <t>70,155</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>2.71%</t>
+          <t>2.74%</t>
         </is>
       </c>
     </row>
@@ -809,12 +809,12 @@
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>44,555</t>
+          <t>48,455</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>2.49%</t>
+          <t>2.53%</t>
         </is>
       </c>
     </row>
@@ -831,12 +831,12 @@
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>19,455</t>
+          <t>21,155</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>2.45%</t>
+          <t>2.44%</t>
         </is>
       </c>
     </row>
@@ -853,12 +853,12 @@
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>18,053</t>
+          <t>19,603</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>2.28%</t>
+          <t>2.24%</t>
         </is>
       </c>
     </row>
@@ -875,12 +875,12 @@
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>76,185</t>
+          <t>82,885</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>1.98%</t>
+          <t>1.97%</t>
         </is>
       </c>
     </row>
@@ -897,12 +897,12 @@
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>31,100</t>
+          <t>33,820</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>1.83%</t>
+          <t>1.84%</t>
         </is>
       </c>
     </row>
@@ -919,12 +919,12 @@
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>20,005</t>
+          <t>21,755</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>1.73%</t>
+          <t>1.72%</t>
         </is>
       </c>
     </row>
@@ -941,7 +941,7 @@
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>50,445</t>
+          <t>54,855</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
@@ -963,12 +963,12 @@
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>19,270</t>
+          <t>20,870</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>1.41%</t>
+          <t>1.38%</t>
         </is>
       </c>
     </row>
@@ -985,56 +985,56 @@
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>11,541</t>
+          <t>12,541</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>1.39%</t>
+          <t>1.36%</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>ETR US</t>
+          <t>ALAB US</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>安特吉公司</t>
+          <t>Astera實驗室公司</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>26,228</t>
+          <t>8,580</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.34%</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>ALAB US</t>
+          <t>ETR US</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>Astera實驗室公司</t>
+          <t>安特吉公司</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>7,860</t>
+          <t>28,428</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>1.29%</t>
+          <t>1.33%</t>
         </is>
       </c>
     </row>
@@ -1051,7 +1051,7 @@
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>35,810</t>
+          <t>38,810</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
@@ -1073,34 +1073,34 @@
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>58,568</t>
+          <t>63,568</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>1.22%</t>
+          <t>1.23%</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>CRWV US</t>
+          <t>C_USD</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>CoreWeave Inc</t>
+          <t>CASH</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>19,467</t>
+          <t>2,530,860</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>1.07%</t>
+          <t>1.09%</t>
         </is>
       </c>
     </row>
@@ -1117,34 +1117,34 @@
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>21,088</t>
+          <t>22,918</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>1.01%</t>
+          <t>1.02%</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>CRDO US</t>
+          <t>CRWV US</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>Credo科技集團控股有限公司</t>
+          <t>CoreWeave Inc</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>9,466</t>
+          <t>21,167</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>1.00%</t>
+          <t>1.01%</t>
         </is>
       </c>
     </row>
@@ -1161,144 +1161,144 @@
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>125,615</t>
+          <t>135,615</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>0.96%</t>
+          <t>0.98%</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>WEC US</t>
+          <t>CRDO US</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>WEC能源集團公司</t>
+          <t>Credo科技集團控股有限公司</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>18,215</t>
+          <t>10,346</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>0.93%</t>
+          <t>0.96%</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>AEE US</t>
+          <t>WEC US</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>阿莫林公司</t>
+          <t>WEC能源集團公司</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>15,701</t>
+          <t>19,805</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>0.78%</t>
+          <t>0.94%</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>NRG US</t>
+          <t>AEE US</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>NRG Energy Inc</t>
+          <t>阿莫林公司</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>11,625</t>
+          <t>17,071</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>0.72%</t>
+          <t>0.78%</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>CNP US</t>
+          <t>NRG US</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>Centerpoint能源</t>
+          <t>NRG Energy Inc</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>37,060</t>
+          <t>12,645</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>0.71%</t>
+          <t>0.73%</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>PPL US</t>
+          <t>CNP US</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>PPL Corp</t>
+          <t>Centerpoint能源</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>42,630</t>
+          <t>40,300</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>0.69%</t>
+          <t>0.72%</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>C_USD</t>
+          <t>PPL US</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>CASH</t>
+          <t>PPL Corp</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>935,766</t>
+          <t>46,360</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>0.43%</t>
+          <t>0.70%</t>
         </is>
       </c>
     </row>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>1,595,093</t>
+          <t>28,710</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr">
